--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C981F14-64DA-4F4E-9C6C-77279BAEFA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D158B9A4-DA5B-47D8-BA12-A608F6B92CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
     <sheet name="WashingtonDatabase" sheetId="16" r:id="rId2"/>
+    <sheet name="MountainDatabase" sheetId="17" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MountainDatabase!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -152,6 +154,15 @@
   </si>
   <si>
     <t>Escala de Cinza</t>
+  </si>
+  <si>
+    <t>Alternative (1)</t>
+  </si>
+  <si>
+    <t>14.16</t>
+  </si>
+  <si>
+    <t>Alternative (2)</t>
   </si>
 </sst>
 </file>
@@ -1903,7 +1914,7 @@
               </c:extLst>
               <c:f>(LennaDatabase!$B$51:$B$54,LennaDatabase!$B$56)</c:f>
               <c:numCache>
-                <c:formatCode>00,000,000,000,000</c:formatCode>
+                <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>24.494897427831699</c:v>
@@ -3610,7 +3621,7 @@
               </c:extLst>
               <c:f>(WashingtonDatabase!$B$37:$B$40,WashingtonDatabase!$B$42)</c:f>
               <c:numCache>
-                <c:formatCode>00,000,000,000,000</c:formatCode>
+                <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>20.445048300260801</c:v>
@@ -4272,6 +4283,1550 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" b="1"/>
+              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.708286735947222E-2"/>
+          <c:y val="9.442161516380955E-2"/>
+          <c:w val="0.92001075377594732"/>
+          <c:h val="0.70519411793005016"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$B$2:$B$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$B$3:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$C$2:$C$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$C$3:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$D$2:$D$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$D$3:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$E$2:$E$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$E$3:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$G$2:$G$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$G$3:$G$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="392150687"/>
+        <c:axId val="392152351"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!$F$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Hsv-Color Hamming</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c:spPr>
+                <c:marker>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!$A$3:$A$21</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>Alternative (1)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Alternative (2)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>MountainDatabase!$F$2:$F$21</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!$F$3:$F$21</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="0">
+                        <c:v>6</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-81B7-4707-84D8-6D04D5AC34BE}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="392150687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Imagens Alteradas</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47140303978943293"/>
+              <c:y val="0.89287472538045831"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392152351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="115"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="392152351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="17"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Distância</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" baseline="0"/>
+                  <a:t> de Hamming</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.9946221881624392E-2"/>
+              <c:y val="0.32089614169566544"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392150687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1.5"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.5704766815327571E-2"/>
+          <c:y val="0.94176582369826323"/>
+          <c:w val="0.82859036688846588"/>
+          <c:h val="5.8234176301736718E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Euclidean Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$B$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Euclidean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$51:$A$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$A$51:$A$54,MountainDatabase!$A$56)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$B$51:$B$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$B$51:$B$54,MountainDatabase!$B$56)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000000000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>24.494897427831699</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.664319132398401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.8605710994917</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.203603311174501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.681120484521699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9BC3-4B1A-B2F2-CEC5D77AFEB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="8"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Manhattan Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$C$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Manhattan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$51:$A$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$A$51:$A$54,MountainDatabase!$A$56)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$C$51:$C$56</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$C$51:$C$54,MountainDatabase!$C$56)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>109.92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-723F-439A-8D41-70363CACAEEC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="15"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4432,6 +5987,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5981,6 +7616,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6712,6 +9379,125 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{333143C3-A6A3-4126-B3DB-947AFACDE60B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>97896</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>137583</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>173303</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607C45D9-D5EB-4756-8E9F-0431DEE9B816}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>14153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>328084</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>177271</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93939A1-03B7-42D0-8182-1C6066367F18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>693870</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>9263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>423332</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>172381</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5390622-FF6C-4796-BDAD-3A05C4FC4A61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7903,4 +10689,341 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="21">
+        <v>0</v>
+      </c>
+      <c r="C3" s="21">
+        <v>2</v>
+      </c>
+      <c r="D3" s="21">
+        <v>2</v>
+      </c>
+      <c r="E3" s="21">
+        <v>2</v>
+      </c>
+      <c r="F3" s="21">
+        <v>6</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="22"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="22"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="15">
+        <v>24.494897427831699</v>
+      </c>
+      <c r="C51" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="15">
+        <v>23.664319132398401</v>
+      </c>
+      <c r="C52" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="15">
+        <v>17.8605710994917</v>
+      </c>
+      <c r="C53" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="15">
+        <v>22.203603311174501</v>
+      </c>
+      <c r="C54" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="15">
+        <v>7.2111025509279703</v>
+      </c>
+      <c r="C55" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="15">
+        <v>36.681120484521699</v>
+      </c>
+      <c r="C56" s="18">
+        <v>109.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D158B9A4-DA5B-47D8-BA12-A608F6B92CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E7C8A7-6582-45C3-82BD-50B9650D17BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -163,6 +163,96 @@
   </si>
   <si>
     <t>Alternative (2)</t>
+  </si>
+  <si>
+    <t>Alternative (3)</t>
+  </si>
+  <si>
+    <t>Alternative (4)</t>
+  </si>
+  <si>
+    <t>Alternative (5)</t>
+  </si>
+  <si>
+    <t>Alternative (6)</t>
+  </si>
+  <si>
+    <t>Alternative (7)</t>
+  </si>
+  <si>
+    <t>Alternative (8)</t>
+  </si>
+  <si>
+    <t>Alternative (9)</t>
+  </si>
+  <si>
+    <t>Alternative (10)</t>
+  </si>
+  <si>
+    <t>Alternative (11)</t>
+  </si>
+  <si>
+    <t>Alternative (12)</t>
+  </si>
+  <si>
+    <t>Alternative (13)</t>
+  </si>
+  <si>
+    <t>Alternative (14)</t>
+  </si>
+  <si>
+    <t>Alternative (15)</t>
+  </si>
+  <si>
+    <t>Alternative (16)</t>
+  </si>
+  <si>
+    <t>Alternative (17)</t>
+  </si>
+  <si>
+    <t>Alternative (18)</t>
+  </si>
+  <si>
+    <t>Alternative (19)</t>
+  </si>
+  <si>
+    <t>Alternative (20)</t>
+  </si>
+  <si>
+    <t>Alternative (21)</t>
+  </si>
+  <si>
+    <t>Alternative (22)</t>
+  </si>
+  <si>
+    <t>Alternative (23)</t>
+  </si>
+  <si>
+    <t>Alternative (24)</t>
+  </si>
+  <si>
+    <t>Alternative (25)</t>
+  </si>
+  <si>
+    <t>Alternative (26)</t>
+  </si>
+  <si>
+    <t>Alternative (27)</t>
+  </si>
+  <si>
+    <t>Alternative (28)</t>
+  </si>
+  <si>
+    <t>Alternative (29)</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>15.16</t>
+  </si>
+  <si>
+    <t>14.66</t>
   </si>
 </sst>
 </file>
@@ -4373,12 +4463,63 @@
               </c:extLst>
               <c:f>MountainDatabase!$A$3:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4397,6 +4538,12 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4434,12 +4581,63 @@
               </c:extLst>
               <c:f>MountainDatabase!$A$3:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4458,6 +4656,12 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -4495,12 +4699,63 @@
               </c:extLst>
               <c:f>MountainDatabase!$A$3:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4520,6 +4775,12 @@
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4556,12 +4817,63 @@
               </c:extLst>
               <c:f>MountainDatabase!$A$3:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4580,6 +4892,12 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -4636,12 +4954,63 @@
               </c:extLst>
               <c:f>MountainDatabase!$A$3:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4660,6 +5029,12 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4739,12 +5114,63 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="2"/>
+                      <c:ptCount val="19"/>
                       <c:pt idx="0">
                         <c:v>Alternative (1)</c:v>
                       </c:pt>
                       <c:pt idx="1">
                         <c:v>Alternative (2)</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Alternative (3)</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Alternative (4)</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Alternative (5)</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Alternative (6)</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Alternative (7)</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Alternative (8)</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Alternative (9)</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>Alternative (10)</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>Alternative (11)</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>Alternative (12)</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>Alternative (13)</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>Alternative (14)</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>Alternative (15)</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>Alternative (16)</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>Alternative (17)</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>Alternative (18)</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>Alternative (19)</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -4766,6 +5192,12 @@
                       <c:ptCount val="19"/>
                       <c:pt idx="0">
                         <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5091,7 +5523,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$B$50</c:f>
+              <c:f>MountainDatabase!$B$62</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5129,11 +5561,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$51:$A$56</c15:sqref>
+                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$A$51:$A$54,MountainDatabase!$A$56)</c:f>
+              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -5159,28 +5591,28 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$51:$B$56</c15:sqref>
+                    <c15:sqref>MountainDatabase!$B$63:$B$68</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$B$51:$B$54,MountainDatabase!$B$56)</c:f>
+              <c:f>(MountainDatabase!$B$63:$B$66,MountainDatabase!$B$68)</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24.494897427831699</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.664319132398401</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.8605710994917</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.203603311174501</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36.681120484521699</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5499,7 +5931,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$C$50</c:f>
+              <c:f>MountainDatabase!$C$62</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5537,11 +5969,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$51:$A$56</c15:sqref>
+                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$A$51:$A$54,MountainDatabase!$A$56)</c:f>
+              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -5567,28 +5999,28 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$51:$C$56</c15:sqref>
+                    <c15:sqref>MountainDatabase!$C$63:$C$68</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$C$51:$C$54,MountainDatabase!$C$56)</c:f>
+              <c:f>(MountainDatabase!$C$63:$C$66,MountainDatabase!$C$68)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>56</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="0">
-                  <c:v>109.92</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9407,13 +9839,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>97896</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>137583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>173303</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9445,13 +9877,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9483,13 +9915,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>9263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>172381</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10693,7 +11125,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -10753,7 +11185,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="21">
@@ -10779,24 +11211,52 @@
       <c r="A4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="B4" s="21">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21">
+        <v>2</v>
+      </c>
+      <c r="F4" s="21">
+        <v>5</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
+      <c r="A5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="21">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>2</v>
+      </c>
+      <c r="F5" s="21">
+        <v>5</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="14" t="s">
+        <v>41</v>
+      </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
@@ -10805,7 +11265,9 @@
       <c r="G6" s="22"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="14" t="s">
+        <v>42</v>
+      </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -10814,7 +11276,9 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
@@ -10823,7 +11287,9 @@
       <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -10832,7 +11298,9 @@
       <c r="G9" s="22"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -10841,7 +11309,9 @@
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="14" t="s">
+        <v>46</v>
+      </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -10850,7 +11320,9 @@
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="B12" s="21"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -10859,7 +11331,9 @@
       <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
@@ -10868,7 +11342,9 @@
       <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="14" t="s">
+        <v>49</v>
+      </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -10877,7 +11353,9 @@
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -10886,7 +11364,9 @@
       <c r="G15" s="22"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="B16" s="21"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -10895,7 +11375,9 @@
       <c r="G16" s="22"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -10904,7 +11386,9 @@
       <c r="G17" s="22"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
@@ -10913,7 +11397,9 @@
       <c r="G18" s="22"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -10922,7 +11408,9 @@
       <c r="G19" s="22"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
@@ -10931,7 +11419,9 @@
       <c r="G20" s="22"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="14" t="s">
+        <v>56</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -10939,81 +11429,202 @@
       <c r="F21" s="1"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="15">
-        <v>24.494897427831699</v>
-      </c>
-      <c r="C51" s="1">
-        <v>56</v>
+      <c r="B63" s="15">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="15">
-        <v>23.664319132398401</v>
-      </c>
-      <c r="C52" s="1">
-        <v>52</v>
+      <c r="B64" s="15">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="15">
-        <v>17.8605710994917</v>
-      </c>
-      <c r="C53" s="1">
-        <v>37</v>
+      <c r="B65" s="15">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="15">
-        <v>22.203603311174501</v>
-      </c>
-      <c r="C54" s="1">
-        <v>47</v>
+      <c r="B66" s="15">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="15">
-        <v>7.2111025509279703</v>
-      </c>
-      <c r="C55" s="1">
-        <v>16</v>
+      <c r="B67" s="15">
+        <v>1</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="15">
-        <v>36.681120484521699</v>
-      </c>
-      <c r="C56" s="18">
-        <v>109.92</v>
+      <c r="B68" s="15">
+        <v>1</v>
+      </c>
+      <c r="C68" s="18">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E7C8A7-6582-45C3-82BD-50B9650D17BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2F988C-C7FA-47EE-8E06-043AFB55710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
-    <sheet name="WashingtonDatabase" sheetId="16" r:id="rId2"/>
-    <sheet name="MountainDatabase" sheetId="17" r:id="rId3"/>
+    <sheet name="MountainDatabase" sheetId="17" r:id="rId2"/>
+    <sheet name="WashingtonDatabase" sheetId="16" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MountainDatabase!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MountainDatabase!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">WashingtonDatabase!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -159,9 +159,6 @@
     <t>Alternative (1)</t>
   </si>
   <si>
-    <t>14.16</t>
-  </si>
-  <si>
     <t>Alternative (2)</t>
   </si>
   <si>
@@ -247,12 +244,6 @@
   </si>
   <si>
     <t>Alternative (30)</t>
-  </si>
-  <si>
-    <t>15.16</t>
-  </si>
-  <si>
-    <t>14.66</t>
   </si>
 </sst>
 </file>
@@ -2725,6 +2716,2330 @@
           <c:x val="6.708286735947222E-2"/>
           <c:y val="9.442161516380955E-2"/>
           <c:w val="0.92001075377594732"/>
+          <c:h val="0.70519411793005016"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$B$2:$B$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$B$2:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$C$3:$C$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$C$3:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$D$3:$D$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$D$3:$D$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$E$3:$E$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$E$3:$E$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hsv-Color Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$F$3:$F$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$F$3:$F$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>Alternative (1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative (2)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alternative (3)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alternative (4)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Alternative (5)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Alternative (6)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Alternative (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Alternative (8)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alternative (9)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alternative (10)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Alternative (11)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Alternative (12)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Alternative (13)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Alternative (14)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Alternative (15)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Alternative (16)</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Alternative (17)</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Alternative (18)</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Alternative (19)</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Alternative (20)</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Alternative (21)</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Alternative (22)</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Alternative (23)</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Alternative (24)</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Alternative (25)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Alternative (26)</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Alternative (27)</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Alternative (28)</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Alternative (29)</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Alternative (30)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$G$3:$G$32</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>MountainDatabase!$G$3:$G$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0" formatCode="0.00">
+                  <c:v>14.16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>14.66</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.00">
+                  <c:v>14.66</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0.00">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-81B7-4707-84D8-6D04D5AC34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="392150687"/>
+        <c:axId val="392152351"/>
+        <c:extLst/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="392150687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Imagens Alteradas</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47140303978943293"/>
+              <c:y val="0.89287472538045831"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392152351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="115"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="392152351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="17"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Distância</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" baseline="0"/>
+                  <a:t> de Hamming</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.9946221881624392E-2"/>
+              <c:y val="0.32089614169566544"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="392150687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1.5"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.5704766815327571E-2"/>
+          <c:y val="0.94176582369826323"/>
+          <c:w val="0.82859036688846588"/>
+          <c:h val="5.8234176301736718E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Euclidean Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$B$62</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Euclidean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$B$63:$B$68</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$B$63:$B$66,MountainDatabase!$B$68)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000000000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9BC3-4B1A-B2F2-CEC5D77AFEB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="8"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Manhattan Distance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MountainDatabase!$C$62</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Manhattan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>A. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>D. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W. Hash Hamming</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>CP Hash Hamming</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>MountainDatabase!$C$63:$C$68</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(MountainDatabase!$C$63:$C$66,MountainDatabase!$C$68)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-723F-439A-8D41-70363CACAEEC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1631798624"/>
+        <c:axId val="1631798208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1631798624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1631798208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1631798624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="15"/>
+        <c:minorUnit val="2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" b="1"/>
+              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.708286735947222E-2"/>
+          <c:y val="9.442161516380955E-2"/>
+          <c:w val="0.92001075377594732"/>
           <c:h val="0.76399145860502204"/>
         </c:manualLayout>
       </c:layout>
@@ -3557,7 +5872,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3965,7 +6280,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4288,1892 +6603,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="12"/>
-        <c:minorUnit val="2"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
-          <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
-          <c:h val="0.70519411793005016"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A. Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$21</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$2:$B$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$B$3:$B$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>P. Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$21</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$2:$C$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$C$3:$C$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="8"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>D. Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$21</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$D$2:$D$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$D$3:$D$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>W. Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$21</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$E$2:$E$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$E$3:$E$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="11"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CP Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="7030A0"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$21</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$G$2:$G$21</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$G$3:$G$21</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="392150687"/>
-        <c:axId val="392152351"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="10"/>
-                <c:order val="4"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>MountainDatabase!$F$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Hsv-Color Hamming</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                  </a:ln>
-                </c:spPr>
-                <c:marker>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                    <a:ln>
-                      <a:solidFill>
-                        <a:schemeClr val="accent6"/>
-                      </a:solidFill>
-                    </a:ln>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>MountainDatabase!$A$2:$A$21</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>MountainDatabase!$A$3:$A$21</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="19"/>
-                      <c:pt idx="0">
-                        <c:v>Alternative (1)</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>Alternative (2)</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>Alternative (3)</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>Alternative (4)</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>Alternative (5)</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>Alternative (6)</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>Alternative (7)</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>Alternative (8)</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>Alternative (9)</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>Alternative (10)</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>Alternative (11)</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>Alternative (12)</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>Alternative (13)</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>Alternative (14)</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>Alternative (15)</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>Alternative (16)</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>Alternative (17)</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>Alternative (18)</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>Alternative (19)</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>MountainDatabase!$F$2:$F$21</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>MountainDatabase!$F$3:$F$21</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="19"/>
-                      <c:pt idx="0">
-                        <c:v>6</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>5</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>5</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000005-81B7-4707-84D8-6D04D5AC34BE}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="392150687"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Imagens Alteradas</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.47140303978943293"/>
-              <c:y val="0.89287472538045831"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="392152351"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="115"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="392152351"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="17"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Distância</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> de Hamming</a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="1.9946221881624392E-2"/>
-              <c:y val="0.32089614169566544"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="392150687"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1.5"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="8.5704766815327571E-2"/>
-          <c:y val="0.94176582369826323"/>
-          <c:w val="0.82859036688846588"/>
-          <c:h val="5.8234176301736718E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Euclidean Distance</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$B$62</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Euclidean</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>A. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>P. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>D. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>W. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>CP Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$63:$B$68</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$B$63:$B$66,MountainDatabase!$B$68)</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000000000000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9BC3-4B1A-B2F2-CEC5D77AFEB1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1631798624"/>
-        <c:axId val="1631798208"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1631798624"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1631798208"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1631798208"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="40"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1631798624"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="8"/>
-        <c:minorUnit val="2"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Manhattan Distance</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!$C$62</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Manhattan</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>A. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>P. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>D. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>W. Hash Hamming</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>CP Hash Hamming</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$63:$C$68</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$C$63:$C$66,MountainDatabase!$C$68)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-723F-439A-8D41-70363CACAEEC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1631798624"/>
-        <c:axId val="1631798208"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1631798624"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1631798208"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1631798208"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="120"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1631798624"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="15"/>
         <c:minorUnit val="2"/>
       </c:valAx>
       <c:spPr>
@@ -9720,6 +10149,125 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>97896</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>137583</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>173303</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607C45D9-D5EB-4756-8E9F-0431DEE9B816}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>14153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>328084</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>177271</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93939A1-03B7-42D0-8182-1C6066367F18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>693870</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>9263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>423332</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>172381</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5390622-FF6C-4796-BDAD-3A05C4FC4A61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>97896</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>137583</xdr:rowOff>
     </xdr:from>
@@ -9811,125 +10359,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{333143C3-A6A3-4126-B3DB-947AFACDE60B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>97896</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>137583</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>173303</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607C45D9-D5EB-4756-8E9F-0431DEE9B816}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>14153</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>177271</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93939A1-03B7-42D0-8182-1C6066367F18}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>9263</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>172381</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5390622-FF6C-4796-BDAD-3A05C4FC4A61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10266,22 +10695,22 @@
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -10836,6 +11265,690 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="21">
+        <v>0</v>
+      </c>
+      <c r="C3" s="21">
+        <v>2</v>
+      </c>
+      <c r="D3" s="21">
+        <v>2</v>
+      </c>
+      <c r="E3" s="21">
+        <v>2</v>
+      </c>
+      <c r="F3" s="21">
+        <v>6</v>
+      </c>
+      <c r="G3" s="22">
+        <v>14.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="21">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21">
+        <v>2</v>
+      </c>
+      <c r="F4" s="21">
+        <v>5</v>
+      </c>
+      <c r="G4" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="21">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>2</v>
+      </c>
+      <c r="F5" s="21">
+        <v>5</v>
+      </c>
+      <c r="G5" s="22">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="21">
+        <v>0</v>
+      </c>
+      <c r="C6" s="21">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21">
+        <v>2</v>
+      </c>
+      <c r="E6" s="21">
+        <v>2</v>
+      </c>
+      <c r="F6" s="21">
+        <v>5</v>
+      </c>
+      <c r="G6" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="21">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21">
+        <v>2</v>
+      </c>
+      <c r="D7" s="21">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>2</v>
+      </c>
+      <c r="F7" s="21">
+        <v>4</v>
+      </c>
+      <c r="G7" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="21">
+        <v>0</v>
+      </c>
+      <c r="C8" s="21">
+        <v>2</v>
+      </c>
+      <c r="D8" s="21">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21">
+        <v>2</v>
+      </c>
+      <c r="F8" s="21">
+        <v>6</v>
+      </c>
+      <c r="G8" s="22">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="21">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21">
+        <v>2</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2</v>
+      </c>
+      <c r="E9" s="21">
+        <v>2</v>
+      </c>
+      <c r="F9" s="21">
+        <v>4</v>
+      </c>
+      <c r="G9" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="21">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21">
+        <v>2</v>
+      </c>
+      <c r="D10" s="21">
+        <v>2</v>
+      </c>
+      <c r="E10" s="21">
+        <v>4</v>
+      </c>
+      <c r="F10" s="21">
+        <v>4</v>
+      </c>
+      <c r="G10" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="21">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21">
+        <v>2</v>
+      </c>
+      <c r="D11" s="21">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21">
+        <v>4</v>
+      </c>
+      <c r="F11" s="21">
+        <v>5</v>
+      </c>
+      <c r="G11" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="21">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20">
+        <v>2</v>
+      </c>
+      <c r="D12" s="20">
+        <v>1</v>
+      </c>
+      <c r="E12" s="20">
+        <v>2</v>
+      </c>
+      <c r="F12" s="21">
+        <v>4</v>
+      </c>
+      <c r="G12" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="21">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21">
+        <v>2</v>
+      </c>
+      <c r="D13" s="21">
+        <v>1</v>
+      </c>
+      <c r="E13" s="21">
+        <v>2</v>
+      </c>
+      <c r="F13" s="21">
+        <v>5</v>
+      </c>
+      <c r="G13" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="21">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21">
+        <v>2</v>
+      </c>
+      <c r="D14" s="21">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21">
+        <v>2</v>
+      </c>
+      <c r="F14" s="21">
+        <v>5</v>
+      </c>
+      <c r="G14" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="21">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21">
+        <v>4</v>
+      </c>
+      <c r="F15" s="21">
+        <v>5</v>
+      </c>
+      <c r="G15" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="21">
+        <v>0</v>
+      </c>
+      <c r="C16" s="20">
+        <v>2</v>
+      </c>
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20">
+        <v>2</v>
+      </c>
+      <c r="F16" s="20">
+        <v>5</v>
+      </c>
+      <c r="G16" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="21">
+        <v>0</v>
+      </c>
+      <c r="C17" s="21">
+        <v>2</v>
+      </c>
+      <c r="D17" s="21">
+        <v>2</v>
+      </c>
+      <c r="E17" s="21">
+        <v>4</v>
+      </c>
+      <c r="F17" s="21">
+        <v>5</v>
+      </c>
+      <c r="G17" s="22">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="21">
+        <v>4</v>
+      </c>
+      <c r="C18" s="21">
+        <v>6</v>
+      </c>
+      <c r="D18" s="21">
+        <v>3</v>
+      </c>
+      <c r="E18" s="21">
+        <v>6</v>
+      </c>
+      <c r="F18" s="21">
+        <v>5</v>
+      </c>
+      <c r="G18" s="22">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4</v>
+      </c>
+      <c r="G21" s="19">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="15">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="15">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" s="15">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="15">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" s="15">
+        <v>1</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="15">
+        <v>1</v>
+      </c>
+      <c r="C68" s="18">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F19D1F8-E0C0-4EE9-B316-914945355609}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10854,22 +11967,22 @@
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -11121,520 +12234,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="21">
-        <v>0</v>
-      </c>
-      <c r="C3" s="21">
-        <v>2</v>
-      </c>
-      <c r="D3" s="21">
-        <v>2</v>
-      </c>
-      <c r="E3" s="21">
-        <v>2</v>
-      </c>
-      <c r="F3" s="21">
-        <v>6</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="21">
-        <v>0</v>
-      </c>
-      <c r="C4" s="21">
-        <v>2</v>
-      </c>
-      <c r="D4" s="21">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21">
-        <v>2</v>
-      </c>
-      <c r="F4" s="21">
-        <v>5</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="21">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21">
-        <v>2</v>
-      </c>
-      <c r="D5" s="21">
-        <v>1</v>
-      </c>
-      <c r="E5" s="21">
-        <v>2</v>
-      </c>
-      <c r="F5" s="21">
-        <v>5</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="22"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="22"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="22"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="19"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="19"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="19"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="19"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="19"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="15">
-        <v>1</v>
-      </c>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="15">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="15">
-        <v>1</v>
-      </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="15">
-        <v>1</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B67" s="15">
-        <v>1</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" s="15">
-        <v>1</v>
-      </c>
-      <c r="C68" s="18">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
-      <sortCondition ref="G1"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2F988C-C7FA-47EE-8E06-043AFB55710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762027F9-45FF-467B-B73E-2108BEA4BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -2905,6 +2905,9 @@
                 <c:pt idx="16">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="19">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3098,6 +3101,9 @@
                 <c:pt idx="15">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3291,6 +3297,9 @@
                 <c:pt idx="15">
                   <c:v>3</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3482,6 +3491,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="18">
@@ -3696,6 +3708,9 @@
                 <c:pt idx="15">
                   <c:v>5</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>4</c:v>
                 </c:pt>
@@ -3907,6 +3922,9 @@
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
                   <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="0.00">
+                  <c:v>15.16</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>15.16</c:v>
@@ -11697,12 +11715,24 @@
       <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
+      <c r="B19" s="21">
+        <v>4</v>
+      </c>
+      <c r="C19" s="21">
+        <v>8</v>
+      </c>
+      <c r="D19" s="21">
+        <v>4</v>
+      </c>
+      <c r="E19" s="21">
+        <v>6</v>
+      </c>
+      <c r="F19" s="21">
+        <v>4</v>
+      </c>
+      <c r="G19" s="22">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">

--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762027F9-45FF-467B-B73E-2108BEA4BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B197DB34-794B-464C-8C55-186FBF6B8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Alternative (29)</t>
-  </si>
-  <si>
-    <t>Alternative (30)</t>
   </si>
 </sst>
 </file>
@@ -2716,7 +2713,7 @@
           <c:x val="6.708286735947222E-2"/>
           <c:y val="9.442161516380955E-2"/>
           <c:w val="0.92001075377594732"/>
-          <c:h val="0.70519411793005016"/>
+          <c:h val="0.67973668596353376"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -2738,16 +2735,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -2834,26 +2824,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$2:$B$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$B$2:$B$31</c:f>
+              <c:f>MountainDatabase!$B$3:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2900,16 +2880,46 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2937,16 +2947,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -3033,26 +3036,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$3:$C$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$C$3:$C$32</c:f>
+              <c:f>MountainDatabase!$C$3:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3104,8 +3097,41 @@
                 <c:pt idx="16">
                   <c:v>8</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>8</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3133,16 +3159,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -3229,26 +3248,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$D$3:$D$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$D$3:$D$32</c:f>
+              <c:f>MountainDatabase!$D$3:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3300,8 +3309,41 @@
                 <c:pt idx="16">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3329,16 +3371,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -3425,26 +3460,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$E$3:$E$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$E$3:$E$32</c:f>
+              <c:f>MountainDatabase!$E$3:$E$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3496,8 +3521,41 @@
                 <c:pt idx="16">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>6</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3544,16 +3602,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -3640,26 +3691,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$F$3:$F$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$F$3:$F$32</c:f>
+              <c:f>MountainDatabase!$F$3:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3711,8 +3752,41 @@
                 <c:pt idx="16">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>7</c:v>
+                </c:pt>
                 <c:pt idx="18">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3759,16 +3833,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$3:$A$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$A$3:$A$32</c:f>
+              <c:f>MountainDatabase!$A$3:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>Alternative (1)</c:v>
                 </c:pt>
@@ -3855,26 +3922,16 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>Alternative (29)</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Alternative (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$G$3:$G$32</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>MountainDatabase!$G$3:$G$32</c:f>
+              <c:f>MountainDatabase!$G$3:$G$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0" formatCode="0.00">
                   <c:v>14.16</c:v>
                 </c:pt>
@@ -3926,7 +3983,40 @@
                 <c:pt idx="16" formatCode="0.00">
                   <c:v>15.16</c:v>
                 </c:pt>
+                <c:pt idx="17" formatCode="0.00">
+                  <c:v>14.66</c:v>
+                </c:pt>
                 <c:pt idx="18" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="0.00">
+                  <c:v>15.33</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="0.00">
+                  <c:v>15.33</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="0.00">
+                  <c:v>15.66</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>15.16</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="0.00">
                   <c:v>15.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -3980,8 +4070,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.47140303978943293"/>
-              <c:y val="0.89287472538045831"/>
+              <c:x val="0.46941254872126892"/>
+              <c:y val="0.90560344136371651"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -4067,7 +4157,7 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> de Hamming</a:t>
+                  <a:t> de Hamming </a:t>
                 </a:r>
                 <a:endParaRPr lang="pt-BR"/>
               </a:p>
@@ -4263,7 +4353,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$B$62</c:f>
+              <c:f>MountainDatabase!$B$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4301,11 +4391,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
+                    <c15:sqref>MountainDatabase!$A$62:$A$67</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
+              <c:f>(MountainDatabase!$A$62:$A$65,MountainDatabase!$A$67)</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -4331,28 +4421,28 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$63:$B$68</c15:sqref>
+                    <c15:sqref>MountainDatabase!$B$62:$B$67</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$B$63:$B$66,MountainDatabase!$B$68)</c:f>
+              <c:f>(MountainDatabase!$B$62:$B$65,MountainDatabase!$B$67)</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>7.1414284285428504</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>21.166010488516701</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>12.2474487139158</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>19.595917942265402</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>81.406961618770595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4446,7 +4536,7 @@
         <c:axId val="1631798208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="40"/>
+          <c:max val="90"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4505,7 +4595,7 @@
         <c:crossAx val="1631798624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="8"/>
+        <c:majorUnit val="15"/>
         <c:minorUnit val="2"/>
       </c:valAx>
       <c:spPr>
@@ -4671,7 +4761,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$C$62</c:f>
+              <c:f>MountainDatabase!$C$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4709,11 +4799,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$63:$A$68</c15:sqref>
+                    <c15:sqref>MountainDatabase!$A$62:$A$67</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$A$63:$A$66,MountainDatabase!$A$68)</c:f>
+              <c:f>(MountainDatabase!$A$62:$A$65,MountainDatabase!$A$67)</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -4739,28 +4829,28 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$63:$C$68</c15:sqref>
+                    <c15:sqref>MountainDatabase!$C$62:$C$67</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(MountainDatabase!$C$63:$C$66,MountainDatabase!$C$68)</c:f>
+              <c:f>(MountainDatabase!$C$62:$C$65,MountainDatabase!$C$67)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="0">
-                  <c:v>1</c:v>
+                  <c:v>438.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4854,7 +4944,7 @@
         <c:axId val="1631798208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="120"/>
+          <c:max val="450"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4913,7 +5003,7 @@
         <c:crossAx val="1631798624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="15"/>
+        <c:majorUnit val="45"/>
         <c:minorUnit val="2"/>
       </c:valAx>
       <c:spPr>
@@ -10166,15 +10256,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>97896</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>137583</xdr:rowOff>
+      <xdr:colOff>87313</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>173303</xdr:rowOff>
+      <xdr:colOff>592667</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>109803</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10205,13 +10295,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10243,13 +10333,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>9263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>172381</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11284,7 +11374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -11738,12 +11828,24 @@
       <c r="A20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="21">
+        <v>8</v>
+      </c>
+      <c r="D20" s="21">
+        <v>4</v>
+      </c>
+      <c r="E20" s="21">
+        <v>6</v>
+      </c>
+      <c r="F20" s="21">
+        <v>7</v>
+      </c>
+      <c r="G20" s="22">
+        <v>14.66</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
@@ -11772,198 +11874,307 @@
       <c r="A22" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="19"/>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="19">
+        <v>15.33</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="19"/>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5</v>
+      </c>
+      <c r="G23" s="19">
+        <v>15.33</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="19"/>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4</v>
+      </c>
+      <c r="G24" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="19"/>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>4</v>
+      </c>
+      <c r="G25" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="19"/>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="19"/>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="19"/>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="19">
+        <v>15.66</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="19"/>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="19">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="19"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="19">
+        <v>15.16</v>
+      </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="19"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>24</v>
+      <c r="A62" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="15">
+        <v>7.1414284285428504</v>
+      </c>
+      <c r="C62" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>11</v>
+      <c r="A63" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B63" s="15">
-        <v>1</v>
+        <v>21.166010488516701</v>
       </c>
       <c r="C63" s="1">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
-        <v>12</v>
+      <c r="A64" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B64" s="15">
-        <v>1</v>
+        <v>12.2474487139158</v>
       </c>
       <c r="C64" s="1">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>13</v>
+      <c r="A65" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="B65" s="15">
-        <v>1</v>
+        <v>19.595917942265402</v>
       </c>
       <c r="C65" s="1">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
-        <v>14</v>
+      <c r="A66" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B66" s="15">
-        <v>1</v>
+        <v>25.7293606605372</v>
       </c>
       <c r="C66" s="1">
-        <v>1</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>16</v>
+      <c r="A67" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="B67" s="15">
-        <v>1</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" s="15">
-        <v>1</v>
-      </c>
-      <c r="C68" s="18">
-        <v>1</v>
+        <v>81.406961618770595</v>
+      </c>
+      <c r="C67" s="18">
+        <v>438.32</v>
       </c>
     </row>
   </sheetData>
